--- a/运气工程/运气工程-02-SlotsRTP计算规则-概述篇.xlsx
+++ b/运气工程/运气工程-02-SlotsRTP计算规则-概述篇.xlsx
@@ -1151,6 +1151,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F66" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1556,6 +1559,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J44" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2012,6 +2018,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M47" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2607,5 +2616,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J54" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/运气工程/运气工程-02-SlotsRTP计算规则-概述篇.xlsx
+++ b/运气工程/运气工程-02-SlotsRTP计算规则-概述篇.xlsx
@@ -410,6 +410,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
+  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -510,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -570,6 +573,18 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1295,7 @@
       <c r="A8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="22">
         <f>SUM(B4:B7)</f>
       </c>
       <c r="C8" s="6" t="s">
@@ -1361,7 +1376,7 @@
       <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="23">
         <f>B8-B12</f>
       </c>
       <c r="C13" s="6" t="s">
@@ -1429,10 +1444,10 @@
       <c r="A17" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="23">
         <f>$B$4</f>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="23">
         <f>B17/$B$8</f>
       </c>
       <c r="D17" s="5" t="s">
@@ -1446,10 +1461,10 @@
       <c r="A18" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="23">
         <f>$B$5</f>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="23">
         <f>B18/$B$8</f>
       </c>
       <c r="D18" s="5" t="s">
@@ -1463,10 +1478,10 @@
       <c r="A19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="23">
         <f>$B$6</f>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="23">
         <f>B19/$B$8</f>
       </c>
       <c r="D19" s="5" t="s">
@@ -1480,10 +1495,10 @@
       <c r="A20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="23">
         <f>$B$7</f>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="23">
         <f>B20/$B$8</f>
       </c>
       <c r="D20" s="5" t="s">
@@ -1497,10 +1512,10 @@
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="24">
         <f>SUM(B17:B20)</f>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="24">
         <f>SUM(C17:C20)</f>
       </c>
       <c r="D21" s="5" t="s">
@@ -1642,7 +1657,7 @@
       <c r="C5" s="16">
         <v>500</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="23">
         <f>B5*C5</f>
       </c>
       <c r="E5" t="s">
@@ -1659,7 +1674,7 @@
       <c r="C6" s="16">
         <v>100</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="23">
         <f>B6*C6</f>
       </c>
       <c r="E6" t="s">
@@ -1676,7 +1691,7 @@
       <c r="C7" s="16">
         <v>200</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="23">
         <f>B7*C7</f>
       </c>
       <c r="E7" t="s">
@@ -1693,7 +1708,7 @@
       <c r="C8" s="16">
         <v>60</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="23">
         <f>B8*C8</f>
       </c>
       <c r="E8" t="s">
@@ -1710,7 +1725,7 @@
       <c r="C9" s="16">
         <v>12</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="23">
         <f>B9*C9</f>
       </c>
       <c r="E9" t="s">
@@ -1727,7 +1742,7 @@
       <c r="C10" s="16">
         <v>40</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="23">
         <f>B10*C10</f>
       </c>
       <c r="E10" t="s">
@@ -1744,7 +1759,7 @@
       <c r="C11" s="16">
         <v>8</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="23">
         <f>B11*C11</f>
       </c>
       <c r="E11" t="s">
@@ -1761,7 +1776,7 @@
       <c r="C12" s="16">
         <v>2</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="23">
         <f>B12*C12</f>
       </c>
       <c r="E12" t="s">
@@ -1778,7 +1793,7 @@
       <c r="C13" s="16">
         <v>3</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="23">
         <f>B13*C13</f>
       </c>
       <c r="E13" t="s">
@@ -1795,7 +1810,7 @@
       <c r="C14" s="16">
         <v>2</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="23">
         <f>B14*C14</f>
       </c>
       <c r="E14" t="s">
@@ -1806,13 +1821,13 @@
       <c r="A15" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="24">
         <f>SUM(B5:B14)</f>
       </c>
       <c r="C15" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="22">
         <f>SUM(D5:D14)</f>
       </c>
       <c r="E15" t="s">
@@ -1855,7 +1870,7 @@
       <c r="A18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="23">
         <f>B15</f>
       </c>
       <c r="C18" s="14" t="s">
@@ -1889,7 +1904,7 @@
       <c r="A20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="23">
         <f>1-B15</f>
       </c>
       <c r="C20" s="14" t="s">
@@ -1957,7 +1972,7 @@
       <c r="A24" t="s">
         <v>99</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="23">
         <f>D15-B23</f>
       </c>
       <c r="C24" s="14" t="s">
@@ -2192,7 +2207,7 @@
       <c r="A10" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="23">
         <f>1-B5</f>
       </c>
       <c r="C10" s="6" t="s">
@@ -2266,7 +2281,7 @@
       <c r="C14" s="19">
         <f>$B$4*B14</f>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="23">
         <f>C14/$B$4</f>
       </c>
       <c r="E14" t="s">
@@ -2283,7 +2298,7 @@
       <c r="C15" s="19">
         <f>$B$4*B15</f>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="23">
         <f>C15/$B$4</f>
       </c>
       <c r="E15" t="s">
@@ -2300,7 +2315,7 @@
       <c r="C16" s="19">
         <f>$B$4*B16</f>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="23">
         <f>C16/$B$4</f>
       </c>
       <c r="E16" t="s">
@@ -2317,7 +2332,7 @@
       <c r="C17" s="19">
         <f>$B$4*B17</f>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="23">
         <f>C17/$B$4</f>
       </c>
       <c r="E17" t="s">
@@ -2328,13 +2343,13 @@
       <c r="A18" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="24">
         <f>SUM(B14:B17)</f>
       </c>
       <c r="C18" s="20">
         <f>SUM(C14:C17)</f>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="24">
         <f>C18/$B$4</f>
       </c>
       <c r="E18" t="s">
@@ -2345,7 +2360,7 @@
       <c r="A19" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="23">
         <f>B18-B5</f>
       </c>
       <c r="C19" s="20" t="s">
@@ -2538,7 +2553,7 @@
       <c r="C30" s="19">
         <f>$B$4-B30</f>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="23">
         <f>C30/$B$4</f>
       </c>
       <c r="E30" s="6" t="s">
@@ -2555,7 +2570,7 @@
       <c r="C31" s="19">
         <f>$B$4-B31</f>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="23">
         <f>C31/$B$4</f>
       </c>
       <c r="E31" s="6" t="s">
@@ -2572,7 +2587,7 @@
       <c r="C32" s="19">
         <f>$B$4-B32</f>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="23">
         <f>C32/$B$4</f>
       </c>
       <c r="E32" s="6" t="s">
@@ -2589,7 +2604,7 @@
       <c r="C33" s="19">
         <f>$B$4-B33</f>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="23">
         <f>C33/$B$4</f>
       </c>
       <c r="E33" t="s">
@@ -2606,7 +2621,7 @@
       <c r="C34" s="19">
         <f>$B$4-B34</f>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="23">
         <f>C34/$B$4</f>
       </c>
       <c r="E34" t="s">
